--- a/output/jr_database/matched_entities_log.xlsx
+++ b/output/jr_database/matched_entities_log.xlsx
@@ -481,103 +481,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gourmantché</t>
+          <t>Mbuti</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>murdock</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GURMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>MORU-MANGBETU AND SERE-MUNDU-SPEAKING PYGMY TRIBES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mbuti</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Gurma_people</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+          <t>https://en.wikipedia.org/wiki/Mbuti_people</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Bira villagers</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>llm_ehraf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:05:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Djerma</t>
+          <t>Punu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>murdock</t>
+          <t>geopr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZERMA</t>
+          <t>ESHIRA/BAPOUNOU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Category:Djerma_people</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+          <t>https://en.wikipedia.org/wiki/Punu_people</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Busansi</t>
+          <t>VILI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:05:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gourounsi</t>
+          <t>Bira villagers</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,45 +583,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GRUNSHI</t>
+          <t>BIRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Gurunsi_people</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Bassorobié</t>
+          <t>Mbuti</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>keerthana_analysis;llm_ehraf</t>
+          <t>llm_ehraf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kurumba</t>
+          <t>Dii</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -635,45 +623,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LILSE</t>
+          <t>DURU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://www.101lasttribes.com/tribes/kurumba.html</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bobo</t>
+          <t>BAYA</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Birifor</t>
+          <t>Imeggedezen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -683,45 +663,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIRIFON</t>
+          <t>EGEDE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.101lasttribes.com/tribes/birifor.html</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+          <t>https://www.101lasttribes.com/tribes/igede.html</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bua</t>
+          <t>all Tuareg</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>llm_ehraf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tiefo</t>
+          <t>Lumbu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -731,45 +707,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SENUFO</t>
+          <t>LUMBO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://www.101lasttribes.com/tribes/tiefo.html</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Birifor</t>
+          <t>VILI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zigua</t>
+          <t>Vingu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -779,7 +747,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZIGULA</t>
+          <t>MBEMBE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -789,11 +757,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BONDEI</t>
+          <t>VILI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -802,14 +770,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mandé</t>
+          <t>all Tuareg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -819,41 +787,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MALINKE</t>
+          <t>AHAGGAREN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Mand%C3%A9_peoples</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bobo</t>
+          <t>Imeggedezen</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>llm_ehraf</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:10:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sambla</t>
+          <t>Kugni</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -863,41 +827,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAMO</t>
+          <t>KUNYI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://joshuaproject.net/people_groups/14813/UV</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bua</t>
+          <t>VILI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:21:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gourounsi (Ko)</t>
+          <t>Mawia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -907,7 +867,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GRUNSHI</t>
+          <t>MAKONDE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -917,37 +877,37 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bobo</t>
+          <t>MBUNGA</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:21:39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gourounsi (Lela)</t>
+          <t>Vumba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>murdock</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GRUNSHI</t>
+          <t>SWAHILI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -957,27 +917,27 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Busansi</t>
+          <t>DIGO</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T12:21:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gurmance</t>
+          <t>Wasili</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -987,34 +947,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GURMA</t>
+          <t>SHUWA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Gurma_people</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dogon</t>
+          <t>KANEMBU</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>keerthana_analysis</t>
+          <t>icmid_sheet2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-31T12:43:03</t>
+          <t>2026-08-21T14:07:07</t>
         </is>
       </c>
     </row>
